--- a/Pure Premium Rates.xlsx
+++ b/Pure Premium Rates.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jadeliang/ASA_Case_Competition/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thuoeamonnoble/Desktop/UDT Case Comp Pure premium rates /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B61AF3E4-3F8E-5642-808E-4D4E41F5ABFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEF4962-94C9-A849-8C61-9743CBD5ADB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7760" yWindow="640" windowWidth="21040" windowHeight="16660" xr2:uid="{F7F8354B-009B-B348-9B4A-FB151E534756}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{F7F8354B-009B-B348-9B4A-FB151E534756}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="31">
   <si>
     <t>Personal Property</t>
   </si>
@@ -72,6 +72,66 @@
   </si>
   <si>
     <t>AVG.</t>
+  </si>
+  <si>
+    <t>Expense and Profit Assumptions</t>
+  </si>
+  <si>
+    <t>Assumption</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Base Variable Expense Ratio</t>
+  </si>
+  <si>
+    <t>Low Expense Case</t>
+  </si>
+  <si>
+    <t>High Expense Case</t>
+  </si>
+  <si>
+    <t>Profit &amp; Contingency</t>
+  </si>
+  <si>
+    <t>Fixed Expense Per Policy</t>
+  </si>
+  <si>
+    <t>Coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pure Premium </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed Expense </t>
+  </si>
+  <si>
+    <t>Profit and Contigency $</t>
+  </si>
+  <si>
+    <t>Variable Expense $</t>
+  </si>
+  <si>
+    <t>Variable Expense %</t>
+  </si>
+  <si>
+    <t>Profit and Contingency %</t>
+  </si>
+  <si>
+    <t>Calculated Gross Premium</t>
+  </si>
+  <si>
+    <t>Sensitivity Anallysis For Different Expense %</t>
+  </si>
+  <si>
+    <t>25% Expense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30% Expense </t>
+  </si>
+  <si>
+    <t>35% Expense</t>
   </si>
 </sst>
 </file>
@@ -79,9 +139,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -123,6 +183,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow (Body)"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -150,194 +231,252 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="55">
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
+  <dxfs count="67">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -356,16 +495,70 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D4F3376E-95A9-2E4A-8EAB-6E4634329F4D}" name="Table1" displayName="Table1" ref="B4:E8" totalsRowCount="1">
   <autoFilter ref="B4:E7" xr:uid="{D4F3376E-95A9-2E4A-8EAB-6E4634329F4D}"/>
   <tableColumns count="4">
-    <tableColumn id="7" xr3:uid="{8918DF95-7C4A-BD41-A5FF-85345C77FC9E}" name="Risk Tier" totalsRowLabel="AVG." dataDxfId="20"/>
-    <tableColumn id="1" xr3:uid="{20E4B2A5-5E98-874B-BBF5-78E2BF4D12EC}" name="Observed" totalsRowFunction="custom" dataDxfId="21" totalsRowDxfId="54">
+    <tableColumn id="7" xr3:uid="{8918DF95-7C4A-BD41-A5FF-85345C77FC9E}" name="Risk Tier" totalsRowLabel="AVG." dataDxfId="66"/>
+    <tableColumn id="1" xr3:uid="{20E4B2A5-5E98-874B-BBF5-78E2BF4D12EC}" name="Observed" totalsRowFunction="custom" dataDxfId="65" totalsRowDxfId="64">
       <totalsRowFormula>SUBTOTAL(1,Table1[Observed] )</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C30DF179-960E-3146-930C-9312F4D27F3B}" name="Fitted" totalsRowFunction="custom" dataDxfId="53" totalsRowDxfId="52">
+    <tableColumn id="2" xr3:uid="{C30DF179-960E-3146-930C-9312F4D27F3B}" name="Fitted" totalsRowFunction="custom" dataDxfId="63" totalsRowDxfId="62">
       <totalsRowFormula>SUBTOTAL(1, Table1[Fitted])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A1053E5A-AEFD-9A43-8AF8-546C5748FC53}" name="Absolute Difference" totalsRowFunction="custom" dataDxfId="51" totalsRowDxfId="50">
+    <tableColumn id="3" xr3:uid="{A1053E5A-AEFD-9A43-8AF8-546C5748FC53}" name="Absolute Difference" totalsRowFunction="custom" dataDxfId="61" totalsRowDxfId="60">
       <calculatedColumnFormula>ABS(Table1[[#This Row],[Observed]]-Table1[[#This Row],[Fitted]])</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(1, Table1[Absolute Difference])</totalsRowFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{0C0745E1-EE26-B44A-B4F7-CE5B08A6DEB8}" name="Table10" displayName="Table10" ref="A47:I59" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="A47:I59" xr:uid="{0C0745E1-EE26-B44A-B4F7-CE5B08A6DEB8}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{6FE62D5D-743F-6045-904C-FCA81B4582F3}" name="Coverage"/>
+    <tableColumn id="2" xr3:uid="{55167134-8067-BD41-A674-DAE5546C6878}" name="Risk Tier"/>
+    <tableColumn id="3" xr3:uid="{A19B608F-48C3-344B-A6DA-0E5DE847B10C}" name="Pure Premium " dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{97ED5E4F-8CE1-B945-8530-5BD596346A27}" name="Fixed Expense " dataDxfId="9">
+      <calculatedColumnFormula>$C$44</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{359992BF-E0D0-1142-B0F9-93DC1CE55142}" name="Variable Expense %" dataDxfId="8">
+      <calculatedColumnFormula>$C$40</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{00884097-3CCC-494C-BB78-990EDEC8C987}" name="Profit and Contingency %" dataDxfId="7">
+      <calculatedColumnFormula>$C$43</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{DD97376C-E5B0-BC4F-806B-FC419502EA94}" name="Calculated Gross Premium" dataDxfId="6">
+      <calculatedColumnFormula>(C48+D48)/(1-E48-F48)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{96FD6BCC-34D2-894F-ADE1-C96B03B25D6D}" name="Variable Expense $" dataDxfId="5">
+      <calculatedColumnFormula>G48*E48</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{160CB168-76B5-5C4C-970E-15211A25735B}" name="Profit and Contigency $" dataDxfId="4">
+      <calculatedColumnFormula>G48*F48</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{033494D3-DDA5-7842-BF0F-48B3F28488BE}" name="Table11" displayName="Table11" ref="A63:E75" totalsRowShown="0">
+  <autoFilter ref="A63:E75" xr:uid="{033494D3-DDA5-7842-BF0F-48B3F28488BE}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{4FA85801-C71E-284D-81FA-B5DEA798AED6}" name="Coverage">
+      <calculatedColumnFormula>A48</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{FBD162EA-0264-9B49-AEF5-E5B6728B36AC}" name="Risk Tier">
+      <calculatedColumnFormula>B48</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{CF2F717C-B478-CF41-B8F3-C28D21541746}" name="25% Expense" dataDxfId="2">
+      <calculatedColumnFormula>(C48+$C$44)/(1-$C$41-$C$43)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{6563BA41-247A-504A-8EB8-604A2B19C1CA}" name="30% Expense " dataDxfId="1">
+      <calculatedColumnFormula>(C48+$C$44)/(1-$C$40-$C$43)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{5BAA57EC-536C-5C44-88CF-2AFC57EA46B8}" name="35% Expense" dataDxfId="0">
+      <calculatedColumnFormula>(C48+$C$44)/(1-$C$42-$C$43)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -376,14 +569,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{910E3987-AA70-DB44-ADDB-934538A07F05}" name="Table13" displayName="Table13" ref="G4:J8" totalsRowCount="1">
   <autoFilter ref="G4:J7" xr:uid="{910E3987-AA70-DB44-ADDB-934538A07F05}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{83712F53-0FC4-9541-8347-965887B62514}" name="Risk Tier" totalsRowLabel="AVG." dataDxfId="2"/>
-    <tableColumn id="1" xr3:uid="{057207C4-5D28-6246-8217-DDFF3EA7336D}" name="Observed" totalsRowFunction="custom" dataDxfId="48" totalsRowDxfId="49">
+    <tableColumn id="4" xr3:uid="{83712F53-0FC4-9541-8347-965887B62514}" name="Risk Tier" totalsRowLabel="AVG." dataDxfId="59"/>
+    <tableColumn id="1" xr3:uid="{057207C4-5D28-6246-8217-DDFF3EA7336D}" name="Observed" totalsRowFunction="custom" dataDxfId="58" totalsRowDxfId="57">
       <totalsRowFormula>SUBTOTAL(1,Table13[Observed] )</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6036E869-A94E-2C4B-9F3E-EDC498F1CF85}" name="Fitted" totalsRowFunction="custom" dataDxfId="46" totalsRowDxfId="47">
+    <tableColumn id="2" xr3:uid="{6036E869-A94E-2C4B-9F3E-EDC498F1CF85}" name="Fitted" totalsRowFunction="custom" dataDxfId="56" totalsRowDxfId="55">
       <totalsRowFormula>SUBTOTAL(1, Table13[Fitted])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{18AB0BAF-F3D8-ED47-8544-D751627AFED9}" name="Absolute Difference" totalsRowFunction="custom" dataDxfId="44" totalsRowDxfId="45">
+    <tableColumn id="3" xr3:uid="{18AB0BAF-F3D8-ED47-8544-D751627AFED9}" name="Absolute Difference" totalsRowFunction="custom" dataDxfId="54" totalsRowDxfId="53">
       <calculatedColumnFormula>ABS(Table13[[#This Row],[Observed]]-Table13[[#This Row],[Fitted]])</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(1, Table13[Absolute Difference])</totalsRowFormula>
     </tableColumn>
@@ -396,14 +589,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{46740DD6-8D3F-4C41-B6C2-EB01A7D9CF95}" name="Table14" displayName="Table14" ref="B13:E17" totalsRowCount="1">
   <autoFilter ref="B13:E16" xr:uid="{46740DD6-8D3F-4C41-B6C2-EB01A7D9CF95}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{607CE2A9-8871-A144-9CAE-C3248A68B0B8}" name="Risk Tier" totalsRowLabel="AVG." dataDxfId="8"/>
-    <tableColumn id="1" xr3:uid="{6E81F88E-C5EA-984F-86A9-83D03CCECDFB}" name="Observed" totalsRowFunction="custom" dataDxfId="42" totalsRowDxfId="43">
+    <tableColumn id="4" xr3:uid="{607CE2A9-8871-A144-9CAE-C3248A68B0B8}" name="Risk Tier" totalsRowLabel="AVG." dataDxfId="52"/>
+    <tableColumn id="1" xr3:uid="{6E81F88E-C5EA-984F-86A9-83D03CCECDFB}" name="Observed" totalsRowFunction="custom" dataDxfId="51" totalsRowDxfId="50">
       <totalsRowFormula>SUBTOTAL(1,Table14[Observed] )</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{511FC660-D43C-E148-B25A-0D488F067D0C}" name="Fitted" totalsRowFunction="custom" dataDxfId="40" totalsRowDxfId="41">
+    <tableColumn id="2" xr3:uid="{511FC660-D43C-E148-B25A-0D488F067D0C}" name="Fitted" totalsRowFunction="custom" dataDxfId="49" totalsRowDxfId="48">
       <totalsRowFormula>SUBTOTAL(1, Table14[Fitted])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{67E1AF87-FA35-B642-A7F4-F969FDE2778F}" name="Absolute Difference" totalsRowFunction="custom" dataDxfId="38" totalsRowDxfId="39">
+    <tableColumn id="3" xr3:uid="{67E1AF87-FA35-B642-A7F4-F969FDE2778F}" name="Absolute Difference" totalsRowFunction="custom" dataDxfId="47" totalsRowDxfId="46">
       <calculatedColumnFormula>ABS(Table14[[#This Row],[Observed]]-Table14[[#This Row],[Fitted]])</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(1, Table14[Absolute Difference])</totalsRowFormula>
     </tableColumn>
@@ -416,14 +609,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F4FC5045-E28C-854F-956C-78108BB54259}" name="Table135" displayName="Table135" ref="G13:J17" totalsRowCount="1">
   <autoFilter ref="G13:J16" xr:uid="{F4FC5045-E28C-854F-956C-78108BB54259}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{9716A5F7-34CF-7044-8EA9-976BF7B4AF3E}" name="Risk Tier" totalsRowLabel="AVG." dataDxfId="3"/>
-    <tableColumn id="1" xr3:uid="{0DC6EE4F-97B4-DB41-ABA3-D37D4C552733}" name="Observed" totalsRowFunction="custom" dataDxfId="1" totalsRowDxfId="37">
+    <tableColumn id="4" xr3:uid="{9716A5F7-34CF-7044-8EA9-976BF7B4AF3E}" name="Risk Tier" totalsRowLabel="AVG." dataDxfId="45"/>
+    <tableColumn id="1" xr3:uid="{0DC6EE4F-97B4-DB41-ABA3-D37D4C552733}" name="Observed" totalsRowFunction="custom" dataDxfId="44" totalsRowDxfId="43">
       <totalsRowFormula>SUBTOTAL(1,Table135[Observed] )</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{293F59A2-CD66-6E46-A2E6-882BA885A121}" name="Fitted" totalsRowFunction="custom" dataDxfId="35" totalsRowDxfId="36">
+    <tableColumn id="2" xr3:uid="{293F59A2-CD66-6E46-A2E6-882BA885A121}" name="Fitted" totalsRowFunction="custom" dataDxfId="42" totalsRowDxfId="41">
       <totalsRowFormula>SUBTOTAL(1, Table135[Fitted])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{28CF6BDB-BFA5-7348-9164-72744C12996E}" name="Absolute Difference" totalsRowFunction="custom" dataDxfId="33" totalsRowDxfId="34">
+    <tableColumn id="3" xr3:uid="{28CF6BDB-BFA5-7348-9164-72744C12996E}" name="Absolute Difference" totalsRowFunction="custom" dataDxfId="40" totalsRowDxfId="39">
       <calculatedColumnFormula>ABS(Table135[[#This Row],[Observed]]-Table135[[#This Row],[Fitted]])</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(1, Table135[Absolute Difference])</totalsRowFormula>
     </tableColumn>
@@ -436,14 +629,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CF19D37E-B4F4-9F4A-9D2C-15A7CBC1976B}" name="Table146" displayName="Table146" ref="B22:E26" totalsRowCount="1">
   <autoFilter ref="B22:E25" xr:uid="{CF19D37E-B4F4-9F4A-9D2C-15A7CBC1976B}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{B7AD1E64-8E3B-BA4A-9091-CBEBB9EF8BC7}" name="Risk Tier" totalsRowLabel="AVG." dataDxfId="7"/>
-    <tableColumn id="1" xr3:uid="{83B2B00C-91EB-D54F-86B5-9E0BEE2CF4ED}" name="Observed" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="32">
+    <tableColumn id="4" xr3:uid="{B7AD1E64-8E3B-BA4A-9091-CBEBB9EF8BC7}" name="Risk Tier" totalsRowLabel="AVG." dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{83B2B00C-91EB-D54F-86B5-9E0BEE2CF4ED}" name="Observed" totalsRowFunction="custom" dataDxfId="37" totalsRowDxfId="36">
       <totalsRowFormula>SUBTOTAL(1,Table146[Observed] )</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E15A4E32-7F86-314E-8A88-7368A7BD5FD5}" name="Fitted" totalsRowFunction="custom" dataDxfId="29" totalsRowDxfId="30">
+    <tableColumn id="2" xr3:uid="{E15A4E32-7F86-314E-8A88-7368A7BD5FD5}" name="Fitted" totalsRowFunction="custom" dataDxfId="35" totalsRowDxfId="34">
       <totalsRowFormula>SUBTOTAL(1, Table146[Fitted])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A81F8271-B94A-D243-9ED7-75FE33998F1A}" name="Absolute Difference" totalsRowFunction="custom" dataDxfId="27" totalsRowDxfId="28">
+    <tableColumn id="3" xr3:uid="{A81F8271-B94A-D243-9ED7-75FE33998F1A}" name="Absolute Difference" totalsRowFunction="custom" dataDxfId="33" totalsRowDxfId="32">
       <calculatedColumnFormula>ABS(Table146[[#This Row],[Observed]]-Table146[[#This Row],[Fitted]])</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(1, Table146[Absolute Difference])</totalsRowFormula>
     </tableColumn>
@@ -456,14 +649,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8E548A50-2E30-1F41-801D-73AA90CC1214}" name="Table1357" displayName="Table1357" ref="G22:J26" totalsRowCount="1">
   <autoFilter ref="G22:J25" xr:uid="{8E548A50-2E30-1F41-801D-73AA90CC1214}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{3676CE37-F7C5-6544-B2E1-AD6F7E521928}" name="Risk Tier" totalsRowLabel="AVG." dataDxfId="4"/>
-    <tableColumn id="1" xr3:uid="{0B5C8307-12B6-7141-B717-BA9D21076B27}" name="Observed" totalsRowFunction="custom" dataDxfId="0" totalsRowDxfId="26">
+    <tableColumn id="4" xr3:uid="{3676CE37-F7C5-6544-B2E1-AD6F7E521928}" name="Risk Tier" totalsRowLabel="AVG." dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{0B5C8307-12B6-7141-B717-BA9D21076B27}" name="Observed" totalsRowFunction="custom" dataDxfId="30" totalsRowDxfId="29">
       <totalsRowFormula>SUBTOTAL(1,Table1357[Observed] )</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DE7E9AF5-BF89-9C49-8D7C-F3E5F4225E72}" name="Fitted" totalsRowFunction="custom" dataDxfId="24" totalsRowDxfId="25">
+    <tableColumn id="2" xr3:uid="{DE7E9AF5-BF89-9C49-8D7C-F3E5F4225E72}" name="Fitted" totalsRowFunction="custom" dataDxfId="28" totalsRowDxfId="27">
       <totalsRowFormula>SUBTOTAL(1, Table1357[Fitted])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{EA1ADE84-28FD-9246-9331-41A77FA34A99}" name="Absolute Difference" totalsRowFunction="custom" dataDxfId="22" totalsRowDxfId="23">
+    <tableColumn id="3" xr3:uid="{EA1ADE84-28FD-9246-9331-41A77FA34A99}" name="Absolute Difference" totalsRowFunction="custom" dataDxfId="26" totalsRowDxfId="25">
       <calculatedColumnFormula>ABS(Table1357[[#This Row],[Observed]]-Table1357[[#This Row],[Fitted]])</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(1, Table1357[Absolute Difference])</totalsRowFormula>
     </tableColumn>
@@ -476,14 +669,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{65368929-C7D0-2948-A26F-DEB45C25689D}" name="Table1468" displayName="Table1468" ref="B31:E35" totalsRowCount="1">
   <autoFilter ref="B31:E34" xr:uid="{65368929-C7D0-2948-A26F-DEB45C25689D}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{4885230C-565A-C04D-9587-4FD90CEA2E29}" name="Risk Tier" totalsRowLabel="AVG." dataDxfId="6"/>
-    <tableColumn id="1" xr3:uid="{ED04F1D2-3D0E-3E45-BB87-9CF5046E5EEC}" name="Observed" totalsRowFunction="custom" dataDxfId="18" totalsRowDxfId="19">
+    <tableColumn id="4" xr3:uid="{4885230C-565A-C04D-9587-4FD90CEA2E29}" name="Risk Tier" totalsRowLabel="AVG." dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{ED04F1D2-3D0E-3E45-BB87-9CF5046E5EEC}" name="Observed" totalsRowFunction="custom" dataDxfId="23" totalsRowDxfId="22">
       <totalsRowFormula>SUBTOTAL(1,Table1468[Observed] )</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9B13236D-C75D-8C4D-AE10-D4400932D993}" name="Fitted" totalsRowFunction="custom" dataDxfId="16" totalsRowDxfId="17">
+    <tableColumn id="2" xr3:uid="{9B13236D-C75D-8C4D-AE10-D4400932D993}" name="Fitted" totalsRowFunction="custom" dataDxfId="21" totalsRowDxfId="20">
       <totalsRowFormula>SUBTOTAL(1, Table1468[Fitted])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{C657DFCB-04FF-0C4E-94C6-80554CDC767B}" name="Absolute Difference" totalsRowFunction="custom" dataDxfId="14" totalsRowDxfId="15">
+    <tableColumn id="3" xr3:uid="{C657DFCB-04FF-0C4E-94C6-80554CDC767B}" name="Absolute Difference" totalsRowFunction="custom" dataDxfId="19" totalsRowDxfId="18">
       <calculatedColumnFormula>ABS(Table1468[[#This Row],[Observed]]-Table1468[[#This Row],[Fitted]])</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(1, Table1468[Absolute Difference])</totalsRowFormula>
     </tableColumn>
@@ -496,17 +689,27 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DCD2530D-7FCF-5D4E-A2C7-81344DD26C03}" name="Table13579" displayName="Table13579" ref="G31:J35" totalsRowCount="1">
   <autoFilter ref="G31:J34" xr:uid="{DCD2530D-7FCF-5D4E-A2C7-81344DD26C03}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{A7F2CDEB-96C0-FB4A-B026-DF16E8F407A6}" name="Risk Tier" totalsRowLabel="AVG." dataDxfId="5"/>
-    <tableColumn id="1" xr3:uid="{85D0452F-EF62-894D-B7FE-2F5B8094F492}" name="Observed" totalsRowFunction="custom" totalsRowDxfId="13">
+    <tableColumn id="4" xr3:uid="{A7F2CDEB-96C0-FB4A-B026-DF16E8F407A6}" name="Risk Tier" totalsRowLabel="AVG." dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{85D0452F-EF62-894D-B7FE-2F5B8094F492}" name="Observed" totalsRowFunction="custom" totalsRowDxfId="16">
       <totalsRowFormula>SUBTOTAL(1,Table13579[Observed] )</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{0E77611A-8825-C545-B8BA-AE93DE82A226}" name="Fitted" totalsRowFunction="custom" dataDxfId="11" totalsRowDxfId="12">
+    <tableColumn id="2" xr3:uid="{0E77611A-8825-C545-B8BA-AE93DE82A226}" name="Fitted" totalsRowFunction="custom" dataDxfId="15" totalsRowDxfId="14">
       <totalsRowFormula>SUBTOTAL(1, Table13579[Fitted])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1D2EB09C-A83F-5849-935C-00EC73D30C1C}" name="Absolute Difference" totalsRowFunction="custom" dataDxfId="9" totalsRowDxfId="10">
+    <tableColumn id="3" xr3:uid="{1D2EB09C-A83F-5849-935C-00EC73D30C1C}" name="Absolute Difference" totalsRowFunction="custom" dataDxfId="13" totalsRowDxfId="12">
       <calculatedColumnFormula>ABS(Table13579[[#This Row],[Observed]]-Table13579[[#This Row],[Fitted]])</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(1, Table13579[Absolute Difference])</totalsRowFormula>
     </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{B2202A76-6735-2F42-ACB3-A6283EEF0713}" name="Table9" displayName="Table9" ref="B39:C44" totalsRowShown="0">
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{3DE73153-6409-8B40-9A59-A9FAE99EE8D8}" name="Assumption"/>
+    <tableColumn id="2" xr3:uid="{1E4E5C47-4F94-B74D-A567-DA21C89E8824}" name="Value" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -829,16 +1032,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB37550D-5AD1-2D48-8A2A-F3BB1CE866C4}">
-  <dimension ref="A2:J35"/>
+  <dimension ref="A2:J75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="25.1640625" customWidth="1"/>
     <col min="3" max="3" width="19.33203125" customWidth="1"/>
     <col min="4" max="4" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.33203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="25.5" customWidth="1"/>
     <col min="8" max="8" width="19.33203125" customWidth="1"/>
+    <col min="9" max="9" width="22.5" customWidth="1"/>
     <col min="10" max="10" width="20.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1392,7 +1597,7 @@
         <v>58.164299999999969</v>
       </c>
     </row>
-    <row r="33" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B33" s="2">
         <v>2</v>
       </c>
@@ -1420,7 +1625,7 @@
         <v>175.43970000000002</v>
       </c>
     </row>
-    <row r="34" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="2">
         <v>3</v>
       </c>
@@ -1448,7 +1653,7 @@
         <v>92.769499999999994</v>
       </c>
     </row>
-    <row r="35" spans="2:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
         <v>10</v>
       </c>
@@ -1480,10 +1685,828 @@
         <v>108.79116666666665</v>
       </c>
     </row>
+    <row r="38" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="11">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" s="11">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="11">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="11">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J47" s="8"/>
+    </row>
+    <row r="48" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48">
+        <f>G5</f>
+        <v>1</v>
+      </c>
+      <c r="C48" s="1">
+        <f>I5</f>
+        <v>99.714039999999997</v>
+      </c>
+      <c r="D48" s="1">
+        <f>$C$44</f>
+        <v>15</v>
+      </c>
+      <c r="E48" s="11">
+        <f>$C$40</f>
+        <v>0.3</v>
+      </c>
+      <c r="F48" s="11">
+        <f>$C$43</f>
+        <v>0.05</v>
+      </c>
+      <c r="G48" s="1">
+        <f>(C48+D48)/(1-E48-F48)</f>
+        <v>176.48313846153849</v>
+      </c>
+      <c r="H48" s="1">
+        <f>G48*E48</f>
+        <v>52.944941538461542</v>
+      </c>
+      <c r="I48" s="1">
+        <f>G48*F48</f>
+        <v>8.8241569230769255</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49">
+        <f>G6</f>
+        <v>2</v>
+      </c>
+      <c r="C49" s="1">
+        <f>I6</f>
+        <v>122.79734999999999</v>
+      </c>
+      <c r="D49" s="1">
+        <f t="shared" ref="D49:D59" si="0">$C$44</f>
+        <v>15</v>
+      </c>
+      <c r="E49" s="11">
+        <f t="shared" ref="E49:E59" si="1">$C$40</f>
+        <v>0.3</v>
+      </c>
+      <c r="F49" s="11">
+        <f t="shared" ref="F49:F59" si="2">$C$43</f>
+        <v>0.05</v>
+      </c>
+      <c r="G49" s="1">
+        <f t="shared" ref="G49:G59" si="3">(C49+D49)/(1-E49-F49)</f>
+        <v>211.99592307692311</v>
+      </c>
+      <c r="H49" s="1">
+        <f t="shared" ref="H49:H59" si="4">G49*E49</f>
+        <v>63.598776923076926</v>
+      </c>
+      <c r="I49" s="1">
+        <f t="shared" ref="I49:I59" si="5">G49*F49</f>
+        <v>10.599796153846157</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50">
+        <f>G7</f>
+        <v>3</v>
+      </c>
+      <c r="C50" s="1">
+        <f>I7</f>
+        <v>102.31882</v>
+      </c>
+      <c r="D50" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E50" s="11">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="F50" s="11">
+        <f t="shared" si="2"/>
+        <v>0.05</v>
+      </c>
+      <c r="G50" s="1">
+        <f t="shared" si="3"/>
+        <v>180.49049230769234</v>
+      </c>
+      <c r="H50" s="1">
+        <f t="shared" si="4"/>
+        <v>54.147147692307698</v>
+      </c>
+      <c r="I50" s="1">
+        <f t="shared" si="5"/>
+        <v>9.0245246153846175</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B51">
+        <f>G14</f>
+        <v>1</v>
+      </c>
+      <c r="C51" s="1">
+        <f>I14</f>
+        <v>256.73</v>
+      </c>
+      <c r="D51" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E51" s="11">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="F51" s="11">
+        <f t="shared" si="2"/>
+        <v>0.05</v>
+      </c>
+      <c r="G51" s="1">
+        <f t="shared" si="3"/>
+        <v>418.04615384615391</v>
+      </c>
+      <c r="H51" s="1">
+        <f t="shared" si="4"/>
+        <v>125.41384615384617</v>
+      </c>
+      <c r="I51" s="1">
+        <f t="shared" si="5"/>
+        <v>20.902307692307698</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B52">
+        <f>G15</f>
+        <v>2</v>
+      </c>
+      <c r="C52" s="1">
+        <f>I16</f>
+        <v>358.49040000000002</v>
+      </c>
+      <c r="D52" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E52" s="11">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="F52" s="11">
+        <f t="shared" si="2"/>
+        <v>0.05</v>
+      </c>
+      <c r="G52" s="1">
+        <f t="shared" si="3"/>
+        <v>574.60061538461548</v>
+      </c>
+      <c r="H52" s="1">
+        <f t="shared" si="4"/>
+        <v>172.38018461538465</v>
+      </c>
+      <c r="I52" s="1">
+        <f t="shared" si="5"/>
+        <v>28.730030769230776</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B53">
+        <f>G16</f>
+        <v>3</v>
+      </c>
+      <c r="C53" s="1">
+        <f>I17</f>
+        <v>318.60186666666669</v>
+      </c>
+      <c r="D53" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E53" s="11">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="F53" s="11">
+        <f t="shared" si="2"/>
+        <v>0.05</v>
+      </c>
+      <c r="G53" s="1">
+        <f t="shared" si="3"/>
+        <v>513.23364102564119</v>
+      </c>
+      <c r="H53" s="1">
+        <f t="shared" si="4"/>
+        <v>153.97009230769234</v>
+      </c>
+      <c r="I53" s="1">
+        <f t="shared" si="5"/>
+        <v>25.66168205128206</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>2</v>
+      </c>
+      <c r="B54">
+        <f>G23</f>
+        <v>1</v>
+      </c>
+      <c r="C54" s="1">
+        <f>I23</f>
+        <v>67.504429999999999</v>
+      </c>
+      <c r="D54" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E54" s="11">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="F54" s="11">
+        <f t="shared" si="2"/>
+        <v>0.05</v>
+      </c>
+      <c r="G54" s="1">
+        <f t="shared" si="3"/>
+        <v>126.92989230769233</v>
+      </c>
+      <c r="H54" s="1">
+        <f t="shared" si="4"/>
+        <v>38.0789676923077</v>
+      </c>
+      <c r="I54" s="1">
+        <f t="shared" si="5"/>
+        <v>6.3464946153846169</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>2</v>
+      </c>
+      <c r="B55">
+        <f>G24</f>
+        <v>2</v>
+      </c>
+      <c r="C55" s="1">
+        <f>I24</f>
+        <v>66.421409999999995</v>
+      </c>
+      <c r="D55" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E55" s="11">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="F55" s="11">
+        <f t="shared" si="2"/>
+        <v>0.05</v>
+      </c>
+      <c r="G55" s="1">
+        <f t="shared" si="3"/>
+        <v>125.2637076923077</v>
+      </c>
+      <c r="H55" s="1">
+        <f t="shared" si="4"/>
+        <v>37.579112307692313</v>
+      </c>
+      <c r="I55" s="1">
+        <f t="shared" si="5"/>
+        <v>6.2631853846153858</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>2</v>
+      </c>
+      <c r="B56">
+        <f>G25</f>
+        <v>3</v>
+      </c>
+      <c r="C56" s="1">
+        <f>I25</f>
+        <v>94.607439999999997</v>
+      </c>
+      <c r="D56" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E56" s="11">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="F56" s="11">
+        <f t="shared" si="2"/>
+        <v>0.05</v>
+      </c>
+      <c r="G56" s="1">
+        <f t="shared" si="3"/>
+        <v>168.62683076923079</v>
+      </c>
+      <c r="H56" s="1">
+        <f t="shared" si="4"/>
+        <v>50.588049230769236</v>
+      </c>
+      <c r="I56" s="1">
+        <f t="shared" si="5"/>
+        <v>8.43134153846154</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57">
+        <f>G32</f>
+        <v>1</v>
+      </c>
+      <c r="C57" s="1">
+        <f>I32</f>
+        <v>356.45429999999999</v>
+      </c>
+      <c r="D57" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E57" s="11">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="F57" s="11">
+        <f t="shared" si="2"/>
+        <v>0.05</v>
+      </c>
+      <c r="G57" s="1">
+        <f t="shared" si="3"/>
+        <v>571.46815384615388</v>
+      </c>
+      <c r="H57" s="1">
+        <f t="shared" si="4"/>
+        <v>171.44044615384615</v>
+      </c>
+      <c r="I57" s="1">
+        <f t="shared" si="5"/>
+        <v>28.573407692307697</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>3</v>
+      </c>
+      <c r="B58">
+        <f>G33</f>
+        <v>2</v>
+      </c>
+      <c r="C58" s="1">
+        <f>I33</f>
+        <v>522.15970000000004</v>
+      </c>
+      <c r="D58" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E58" s="11">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="F58" s="11">
+        <f t="shared" si="2"/>
+        <v>0.05</v>
+      </c>
+      <c r="G58" s="1">
+        <f t="shared" si="3"/>
+        <v>826.39953846153867</v>
+      </c>
+      <c r="H58" s="1">
+        <f t="shared" si="4"/>
+        <v>247.91986153846159</v>
+      </c>
+      <c r="I58" s="1">
+        <f t="shared" si="5"/>
+        <v>41.319976923076936</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59">
+        <f>G34</f>
+        <v>3</v>
+      </c>
+      <c r="C59" s="1">
+        <f>I34</f>
+        <v>490.80950000000001</v>
+      </c>
+      <c r="D59" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E59" s="11">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="F59" s="11">
+        <f t="shared" si="2"/>
+        <v>0.05</v>
+      </c>
+      <c r="G59" s="1">
+        <f t="shared" si="3"/>
+        <v>778.16846153846166</v>
+      </c>
+      <c r="H59" s="1">
+        <f t="shared" si="4"/>
+        <v>233.45053846153849</v>
+      </c>
+      <c r="I59" s="1">
+        <f t="shared" si="5"/>
+        <v>38.908423076923086</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B62" s="13"/>
+    </row>
+    <row r="63" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>19</v>
+      </c>
+      <c r="B63" t="s">
+        <v>9</v>
+      </c>
+      <c r="C63" t="s">
+        <v>28</v>
+      </c>
+      <c r="D63" t="s">
+        <v>29</v>
+      </c>
+      <c r="E63" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" t="str">
+        <f>A48</f>
+        <v>Personal Property</v>
+      </c>
+      <c r="B64">
+        <f>B48</f>
+        <v>1</v>
+      </c>
+      <c r="C64" s="1">
+        <f>(C48+$C$44)/(1-$C$41-$C$43)</f>
+        <v>163.87720000000002</v>
+      </c>
+      <c r="D64" s="1">
+        <f>(C48+$C$44)/(1-$C$40-$C$43)</f>
+        <v>176.48313846153849</v>
+      </c>
+      <c r="E64" s="1">
+        <f>(C48+$C$44)/(1-$C$42-$C$43)</f>
+        <v>191.19006666666667</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" t="str">
+        <f t="shared" ref="A65:B69" si="6">A49</f>
+        <v>Personal Property</v>
+      </c>
+      <c r="B65">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="C65" s="1">
+        <f t="shared" ref="C65:C75" si="7">(C49+$C$44)/(1-$C$41-$C$43)</f>
+        <v>196.85335714285713</v>
+      </c>
+      <c r="D65" s="1">
+        <f t="shared" ref="D65:D75" si="8">(C49+$C$44)/(1-$C$40-$C$43)</f>
+        <v>211.99592307692311</v>
+      </c>
+      <c r="E65" s="1">
+        <f t="shared" ref="E65:E72" si="9">(C49+$C$44)/(1-$C$42-$C$43)</f>
+        <v>229.66225</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" t="str">
+        <f t="shared" si="6"/>
+        <v>Personal Property</v>
+      </c>
+      <c r="B66">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="C66" s="1">
+        <f t="shared" si="7"/>
+        <v>167.59831428571431</v>
+      </c>
+      <c r="D66" s="1">
+        <f t="shared" si="8"/>
+        <v>180.49049230769234</v>
+      </c>
+      <c r="E66" s="1">
+        <f t="shared" si="9"/>
+        <v>195.53136666666668</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" t="str">
+        <f t="shared" si="6"/>
+        <v>Additional Living Expenses</v>
+      </c>
+      <c r="B67">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="C67" s="1">
+        <f t="shared" si="7"/>
+        <v>388.18571428571431</v>
+      </c>
+      <c r="D67" s="1">
+        <f t="shared" si="8"/>
+        <v>418.04615384615391</v>
+      </c>
+      <c r="E67" s="1">
+        <f t="shared" si="9"/>
+        <v>452.88333333333338</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" t="str">
+        <f t="shared" si="6"/>
+        <v>Additional Living Expenses</v>
+      </c>
+      <c r="B68">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="C68" s="1">
+        <f t="shared" si="7"/>
+        <v>533.55771428571438</v>
+      </c>
+      <c r="D68" s="1">
+        <f t="shared" si="8"/>
+        <v>574.60061538461548</v>
+      </c>
+      <c r="E68" s="1">
+        <f t="shared" si="9"/>
+        <v>622.48400000000004</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" t="str">
+        <f t="shared" si="6"/>
+        <v>Additional Living Expenses</v>
+      </c>
+      <c r="B69">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="C69" s="1">
+        <f t="shared" si="7"/>
+        <v>476.57409523809531</v>
+      </c>
+      <c r="D69" s="1">
+        <f t="shared" si="8"/>
+        <v>513.23364102564119</v>
+      </c>
+      <c r="E69" s="1">
+        <f t="shared" si="9"/>
+        <v>556.00311111111114</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" t="str">
+        <f t="shared" ref="A65:B75" si="10">A54</f>
+        <v>Liability Protection</v>
+      </c>
+      <c r="B70">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="C70" s="1">
+        <f t="shared" si="7"/>
+        <v>117.86347142857143</v>
+      </c>
+      <c r="D70" s="1">
+        <f t="shared" si="8"/>
+        <v>126.92989230769233</v>
+      </c>
+      <c r="E70" s="1">
+        <f t="shared" si="9"/>
+        <v>137.50738333333334</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" t="str">
+        <f t="shared" si="10"/>
+        <v>Liability Protection</v>
+      </c>
+      <c r="B71">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="C71" s="1">
+        <f t="shared" si="7"/>
+        <v>116.3163</v>
+      </c>
+      <c r="D71" s="1">
+        <f t="shared" si="8"/>
+        <v>125.2637076923077</v>
+      </c>
+      <c r="E71" s="1">
+        <f t="shared" si="9"/>
+        <v>135.70235</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" t="str">
+        <f t="shared" si="10"/>
+        <v>Liability Protection</v>
+      </c>
+      <c r="B72">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="C72" s="1">
+        <f t="shared" si="7"/>
+        <v>156.58205714285714</v>
+      </c>
+      <c r="D72" s="1">
+        <f t="shared" si="8"/>
+        <v>168.62683076923079</v>
+      </c>
+      <c r="E72" s="1">
+        <f t="shared" si="9"/>
+        <v>182.67906666666667</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" t="str">
+        <f t="shared" si="10"/>
+        <v>Guest Medical Protection</v>
+      </c>
+      <c r="B73">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="C73" s="1">
+        <f t="shared" si="7"/>
+        <v>530.649</v>
+      </c>
+      <c r="D73" s="1">
+        <f t="shared" si="8"/>
+        <v>571.46815384615388</v>
+      </c>
+      <c r="E73" s="1">
+        <f t="shared" ref="E73:E75" si="11">(C57+$C$44)/(1-$C$42-$C$43)</f>
+        <v>619.09050000000002</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" t="str">
+        <f t="shared" si="10"/>
+        <v>Guest Medical Protection</v>
+      </c>
+      <c r="B74">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="C74" s="1">
+        <f t="shared" si="7"/>
+        <v>767.37100000000009</v>
+      </c>
+      <c r="D74" s="1">
+        <f t="shared" si="8"/>
+        <v>826.39953846153867</v>
+      </c>
+      <c r="E74" s="1">
+        <f t="shared" si="11"/>
+        <v>895.26616666666678</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" t="str">
+        <f t="shared" si="10"/>
+        <v>Guest Medical Protection</v>
+      </c>
+      <c r="B75">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="C75" s="1">
+        <f t="shared" si="7"/>
+        <v>722.58500000000004</v>
+      </c>
+      <c r="D75" s="1">
+        <f t="shared" si="8"/>
+        <v>778.16846153846166</v>
+      </c>
+      <c r="E75" s="1">
+        <f t="shared" si="11"/>
+        <v>843.01583333333338</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A62:B62"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="8">
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <tableParts count="11">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
@@ -1492,6 +2515,9 @@
     <tablePart r:id="rId6"/>
     <tablePart r:id="rId7"/>
     <tablePart r:id="rId8"/>
+    <tablePart r:id="rId9"/>
+    <tablePart r:id="rId10"/>
+    <tablePart r:id="rId11"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Pure Premium Rates.xlsx
+++ b/Pure Premium Rates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thuoeamonnoble/Desktop/UDT Case Comp Pure premium rates /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEF4962-94C9-A849-8C61-9743CBD5ADB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D56649-7E8E-FF40-8DCF-084137F57399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{F7F8354B-009B-B348-9B4A-FB151E534756}"/>
   </bookViews>
@@ -259,12 +259,6 @@
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -295,6 +289,12 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
@@ -512,29 +512,29 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{0C0745E1-EE26-B44A-B4F7-CE5B08A6DEB8}" name="Table10" displayName="Table10" ref="A47:I59" totalsRowShown="0" headerRowDxfId="3">
-  <autoFilter ref="A47:I59" xr:uid="{0C0745E1-EE26-B44A-B4F7-CE5B08A6DEB8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{0C0745E1-EE26-B44A-B4F7-CE5B08A6DEB8}" name="Table10" displayName="Table10" ref="B47:J59" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="B47:J59" xr:uid="{0C0745E1-EE26-B44A-B4F7-CE5B08A6DEB8}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{6FE62D5D-743F-6045-904C-FCA81B4582F3}" name="Coverage"/>
     <tableColumn id="2" xr3:uid="{55167134-8067-BD41-A674-DAE5546C6878}" name="Risk Tier"/>
-    <tableColumn id="3" xr3:uid="{A19B608F-48C3-344B-A6DA-0E5DE847B10C}" name="Pure Premium " dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{97ED5E4F-8CE1-B945-8530-5BD596346A27}" name="Fixed Expense " dataDxfId="9">
+    <tableColumn id="3" xr3:uid="{A19B608F-48C3-344B-A6DA-0E5DE847B10C}" name="Pure Premium " dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{97ED5E4F-8CE1-B945-8530-5BD596346A27}" name="Fixed Expense " dataDxfId="7">
       <calculatedColumnFormula>$C$44</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{359992BF-E0D0-1142-B0F9-93DC1CE55142}" name="Variable Expense %" dataDxfId="8">
+    <tableColumn id="5" xr3:uid="{359992BF-E0D0-1142-B0F9-93DC1CE55142}" name="Variable Expense %" dataDxfId="6">
       <calculatedColumnFormula>$C$40</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00884097-3CCC-494C-BB78-990EDEC8C987}" name="Profit and Contingency %" dataDxfId="7">
+    <tableColumn id="6" xr3:uid="{00884097-3CCC-494C-BB78-990EDEC8C987}" name="Profit and Contingency %" dataDxfId="5">
       <calculatedColumnFormula>$C$43</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{DD97376C-E5B0-BC4F-806B-FC419502EA94}" name="Calculated Gross Premium" dataDxfId="6">
-      <calculatedColumnFormula>(C48+D48)/(1-E48-F48)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="8" xr3:uid="{96FD6BCC-34D2-894F-ADE1-C96B03B25D6D}" name="Variable Expense $" dataDxfId="5">
-      <calculatedColumnFormula>G48*E48</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{160CB168-76B5-5C4C-970E-15211A25735B}" name="Profit and Contigency $" dataDxfId="4">
-      <calculatedColumnFormula>G48*F48</calculatedColumnFormula>
+    <tableColumn id="7" xr3:uid="{DD97376C-E5B0-BC4F-806B-FC419502EA94}" name="Calculated Gross Premium" dataDxfId="4">
+      <calculatedColumnFormula>(D48+E48)/(1-F48-G48)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{96FD6BCC-34D2-894F-ADE1-C96B03B25D6D}" name="Variable Expense $" dataDxfId="3">
+      <calculatedColumnFormula>H48*F48</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{160CB168-76B5-5C4C-970E-15211A25735B}" name="Profit and Contigency $" dataDxfId="2">
+      <calculatedColumnFormula>H48*G48</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -542,23 +542,23 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{033494D3-DDA5-7842-BF0F-48B3F28488BE}" name="Table11" displayName="Table11" ref="A63:E75" totalsRowShown="0">
-  <autoFilter ref="A63:E75" xr:uid="{033494D3-DDA5-7842-BF0F-48B3F28488BE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{033494D3-DDA5-7842-BF0F-48B3F28488BE}" name="Table11" displayName="Table11" ref="B63:F75" totalsRowShown="0">
+  <autoFilter ref="B63:F75" xr:uid="{033494D3-DDA5-7842-BF0F-48B3F28488BE}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{4FA85801-C71E-284D-81FA-B5DEA798AED6}" name="Coverage">
-      <calculatedColumnFormula>A48</calculatedColumnFormula>
+      <calculatedColumnFormula>B48</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{FBD162EA-0264-9B49-AEF5-E5B6728B36AC}" name="Risk Tier">
-      <calculatedColumnFormula>B48</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" xr3:uid="{CF2F717C-B478-CF41-B8F3-C28D21541746}" name="25% Expense" dataDxfId="2">
-      <calculatedColumnFormula>(C48+$C$44)/(1-$C$41-$C$43)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{6563BA41-247A-504A-8EB8-604A2B19C1CA}" name="30% Expense " dataDxfId="1">
-      <calculatedColumnFormula>(C48+$C$44)/(1-$C$40-$C$43)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="5" xr3:uid="{5BAA57EC-536C-5C44-88CF-2AFC57EA46B8}" name="35% Expense" dataDxfId="0">
-      <calculatedColumnFormula>(C48+$C$44)/(1-$C$42-$C$43)</calculatedColumnFormula>
+      <calculatedColumnFormula>C48</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{CF2F717C-B478-CF41-B8F3-C28D21541746}" name="25% Expense" dataDxfId="10">
+      <calculatedColumnFormula>(D48+$C$44)/(1-$C$41-$C$43)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{6563BA41-247A-504A-8EB8-604A2B19C1CA}" name="30% Expense " dataDxfId="9">
+      <calculatedColumnFormula>(D48+$C$44)/(1-$C$40-$C$43)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{5BAA57EC-536C-5C44-88CF-2AFC57EA46B8}" name="35% Expense" dataDxfId="8">
+      <calculatedColumnFormula>(D48+$C$44)/(1-$C$42-$C$43)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1739,763 +1739,762 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="8" t="s">
+      <c r="B47" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="C47" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="D47" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="E47" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="F47" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="G47" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="G47" s="12" t="s">
+      <c r="H47" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="H47" s="8" t="s">
+      <c r="I47" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I47" s="8" t="s">
+      <c r="J47" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J47" s="8"/>
     </row>
     <row r="48" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
+      <c r="B48" t="s">
         <v>0</v>
       </c>
-      <c r="B48">
+      <c r="C48">
         <f>G5</f>
         <v>1</v>
       </c>
-      <c r="C48" s="1">
+      <c r="D48" s="1">
         <f>I5</f>
         <v>99.714039999999997</v>
       </c>
-      <c r="D48" s="1">
+      <c r="E48" s="1">
         <f>$C$44</f>
         <v>15</v>
       </c>
-      <c r="E48" s="11">
+      <c r="F48" s="11">
         <f>$C$40</f>
         <v>0.3</v>
       </c>
-      <c r="F48" s="11">
+      <c r="G48" s="11">
         <f>$C$43</f>
         <v>0.05</v>
       </c>
-      <c r="G48" s="1">
-        <f>(C48+D48)/(1-E48-F48)</f>
+      <c r="H48" s="1">
+        <f>(D48+E48)/(1-F48-G48)</f>
         <v>176.48313846153849</v>
       </c>
-      <c r="H48" s="1">
-        <f>G48*E48</f>
+      <c r="I48" s="1">
+        <f>H48*F48</f>
         <v>52.944941538461542</v>
       </c>
-      <c r="I48" s="1">
-        <f>G48*F48</f>
+      <c r="J48" s="1">
+        <f>H48*G48</f>
         <v>8.8241569230769255</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+    <row r="49" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" t="s">
         <v>0</v>
       </c>
-      <c r="B49">
+      <c r="C49">
         <f>G6</f>
         <v>2</v>
       </c>
-      <c r="C49" s="1">
+      <c r="D49" s="1">
         <f>I6</f>
         <v>122.79734999999999</v>
       </c>
-      <c r="D49" s="1">
-        <f t="shared" ref="D49:D59" si="0">$C$44</f>
+      <c r="E49" s="1">
+        <f t="shared" ref="E49:F59" si="0">$C$44</f>
         <v>15</v>
       </c>
-      <c r="E49" s="11">
-        <f t="shared" ref="E49:E59" si="1">$C$40</f>
+      <c r="F49" s="11">
+        <f t="shared" ref="F49:G59" si="1">$C$40</f>
         <v>0.3</v>
       </c>
-      <c r="F49" s="11">
-        <f t="shared" ref="F49:F59" si="2">$C$43</f>
+      <c r="G49" s="11">
+        <f t="shared" ref="G49:H59" si="2">$C$43</f>
         <v>0.05</v>
       </c>
-      <c r="G49" s="1">
-        <f t="shared" ref="G49:G59" si="3">(C49+D49)/(1-E49-F49)</f>
+      <c r="H49" s="1">
+        <f t="shared" ref="H49:H59" si="3">(D49+E49)/(1-F49-G49)</f>
         <v>211.99592307692311</v>
       </c>
-      <c r="H49" s="1">
-        <f t="shared" ref="H49:H59" si="4">G49*E49</f>
+      <c r="I49" s="1">
+        <f t="shared" ref="I49:I59" si="4">H49*F49</f>
         <v>63.598776923076926</v>
       </c>
-      <c r="I49" s="1">
-        <f t="shared" ref="I49:I59" si="5">G49*F49</f>
+      <c r="J49" s="1">
+        <f t="shared" ref="J49:J59" si="5">H49*G49</f>
         <v>10.599796153846157</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
+    <row r="50" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B50" t="s">
         <v>0</v>
       </c>
-      <c r="B50">
+      <c r="C50">
         <f>G7</f>
         <v>3</v>
       </c>
-      <c r="C50" s="1">
+      <c r="D50" s="1">
         <f>I7</f>
         <v>102.31882</v>
       </c>
-      <c r="D50" s="1">
+      <c r="E50" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E50" s="11">
+      <c r="F50" s="11">
         <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
-      <c r="F50" s="11">
+      <c r="G50" s="11">
         <f t="shared" si="2"/>
         <v>0.05</v>
       </c>
-      <c r="G50" s="1">
+      <c r="H50" s="1">
         <f t="shared" si="3"/>
         <v>180.49049230769234</v>
       </c>
-      <c r="H50" s="1">
+      <c r="I50" s="1">
         <f t="shared" si="4"/>
         <v>54.147147692307698</v>
       </c>
-      <c r="I50" s="1">
+      <c r="J50" s="1">
         <f t="shared" si="5"/>
         <v>9.0245246153846175</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
+    <row r="51" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" t="s">
         <v>1</v>
       </c>
-      <c r="B51">
+      <c r="C51">
         <f>G14</f>
         <v>1</v>
       </c>
-      <c r="C51" s="1">
+      <c r="D51" s="1">
         <f>I14</f>
         <v>256.73</v>
       </c>
-      <c r="D51" s="1">
+      <c r="E51" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E51" s="11">
+      <c r="F51" s="11">
         <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
-      <c r="F51" s="11">
+      <c r="G51" s="11">
         <f t="shared" si="2"/>
         <v>0.05</v>
       </c>
-      <c r="G51" s="1">
+      <c r="H51" s="1">
         <f t="shared" si="3"/>
         <v>418.04615384615391</v>
       </c>
-      <c r="H51" s="1">
+      <c r="I51" s="1">
         <f t="shared" si="4"/>
         <v>125.41384615384617</v>
       </c>
-      <c r="I51" s="1">
+      <c r="J51" s="1">
         <f t="shared" si="5"/>
         <v>20.902307692307698</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
+    <row r="52" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" t="s">
         <v>1</v>
       </c>
-      <c r="B52">
+      <c r="C52">
         <f>G15</f>
         <v>2</v>
       </c>
-      <c r="C52" s="1">
+      <c r="D52" s="1">
         <f>I16</f>
         <v>358.49040000000002</v>
       </c>
-      <c r="D52" s="1">
+      <c r="E52" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E52" s="11">
+      <c r="F52" s="11">
         <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
-      <c r="F52" s="11">
+      <c r="G52" s="11">
         <f t="shared" si="2"/>
         <v>0.05</v>
       </c>
-      <c r="G52" s="1">
+      <c r="H52" s="1">
         <f t="shared" si="3"/>
         <v>574.60061538461548</v>
       </c>
-      <c r="H52" s="1">
+      <c r="I52" s="1">
         <f t="shared" si="4"/>
         <v>172.38018461538465</v>
       </c>
-      <c r="I52" s="1">
+      <c r="J52" s="1">
         <f t="shared" si="5"/>
         <v>28.730030769230776</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
+    <row r="53" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" t="s">
         <v>1</v>
       </c>
-      <c r="B53">
+      <c r="C53">
         <f>G16</f>
         <v>3</v>
       </c>
-      <c r="C53" s="1">
+      <c r="D53" s="1">
         <f>I17</f>
         <v>318.60186666666669</v>
       </c>
-      <c r="D53" s="1">
+      <c r="E53" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E53" s="11">
+      <c r="F53" s="11">
         <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
-      <c r="F53" s="11">
+      <c r="G53" s="11">
         <f t="shared" si="2"/>
         <v>0.05</v>
       </c>
-      <c r="G53" s="1">
+      <c r="H53" s="1">
         <f t="shared" si="3"/>
         <v>513.23364102564119</v>
       </c>
-      <c r="H53" s="1">
+      <c r="I53" s="1">
         <f t="shared" si="4"/>
         <v>153.97009230769234</v>
       </c>
-      <c r="I53" s="1">
+      <c r="J53" s="1">
         <f t="shared" si="5"/>
         <v>25.66168205128206</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
+    <row r="54" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" t="s">
         <v>2</v>
       </c>
-      <c r="B54">
+      <c r="C54">
         <f>G23</f>
         <v>1</v>
       </c>
-      <c r="C54" s="1">
+      <c r="D54" s="1">
         <f>I23</f>
         <v>67.504429999999999</v>
       </c>
-      <c r="D54" s="1">
+      <c r="E54" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E54" s="11">
+      <c r="F54" s="11">
         <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
-      <c r="F54" s="11">
+      <c r="G54" s="11">
         <f t="shared" si="2"/>
         <v>0.05</v>
       </c>
-      <c r="G54" s="1">
+      <c r="H54" s="1">
         <f t="shared" si="3"/>
         <v>126.92989230769233</v>
       </c>
-      <c r="H54" s="1">
+      <c r="I54" s="1">
         <f t="shared" si="4"/>
         <v>38.0789676923077</v>
       </c>
-      <c r="I54" s="1">
+      <c r="J54" s="1">
         <f t="shared" si="5"/>
         <v>6.3464946153846169</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
+    <row r="55" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" t="s">
         <v>2</v>
       </c>
-      <c r="B55">
+      <c r="C55">
         <f>G24</f>
         <v>2</v>
       </c>
-      <c r="C55" s="1">
+      <c r="D55" s="1">
         <f>I24</f>
         <v>66.421409999999995</v>
       </c>
-      <c r="D55" s="1">
+      <c r="E55" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E55" s="11">
+      <c r="F55" s="11">
         <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
-      <c r="F55" s="11">
+      <c r="G55" s="11">
         <f t="shared" si="2"/>
         <v>0.05</v>
       </c>
-      <c r="G55" s="1">
+      <c r="H55" s="1">
         <f t="shared" si="3"/>
         <v>125.2637076923077</v>
       </c>
-      <c r="H55" s="1">
+      <c r="I55" s="1">
         <f t="shared" si="4"/>
         <v>37.579112307692313</v>
       </c>
-      <c r="I55" s="1">
+      <c r="J55" s="1">
         <f t="shared" si="5"/>
         <v>6.2631853846153858</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
+    <row r="56" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" t="s">
         <v>2</v>
       </c>
-      <c r="B56">
+      <c r="C56">
         <f>G25</f>
         <v>3</v>
       </c>
-      <c r="C56" s="1">
+      <c r="D56" s="1">
         <f>I25</f>
         <v>94.607439999999997</v>
       </c>
-      <c r="D56" s="1">
+      <c r="E56" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E56" s="11">
+      <c r="F56" s="11">
         <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
-      <c r="F56" s="11">
+      <c r="G56" s="11">
         <f t="shared" si="2"/>
         <v>0.05</v>
       </c>
-      <c r="G56" s="1">
+      <c r="H56" s="1">
         <f t="shared" si="3"/>
         <v>168.62683076923079</v>
       </c>
-      <c r="H56" s="1">
+      <c r="I56" s="1">
         <f t="shared" si="4"/>
         <v>50.588049230769236</v>
       </c>
-      <c r="I56" s="1">
+      <c r="J56" s="1">
         <f t="shared" si="5"/>
         <v>8.43134153846154</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
+    <row r="57" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" t="s">
         <v>3</v>
       </c>
-      <c r="B57">
+      <c r="C57">
         <f>G32</f>
         <v>1</v>
       </c>
-      <c r="C57" s="1">
+      <c r="D57" s="1">
         <f>I32</f>
         <v>356.45429999999999</v>
       </c>
-      <c r="D57" s="1">
+      <c r="E57" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E57" s="11">
+      <c r="F57" s="11">
         <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
-      <c r="F57" s="11">
+      <c r="G57" s="11">
         <f t="shared" si="2"/>
         <v>0.05</v>
       </c>
-      <c r="G57" s="1">
+      <c r="H57" s="1">
         <f t="shared" si="3"/>
         <v>571.46815384615388</v>
       </c>
-      <c r="H57" s="1">
+      <c r="I57" s="1">
         <f t="shared" si="4"/>
         <v>171.44044615384615</v>
       </c>
-      <c r="I57" s="1">
+      <c r="J57" s="1">
         <f t="shared" si="5"/>
         <v>28.573407692307697</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
+    <row r="58" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" t="s">
         <v>3</v>
       </c>
-      <c r="B58">
+      <c r="C58">
         <f>G33</f>
         <v>2</v>
       </c>
-      <c r="C58" s="1">
+      <c r="D58" s="1">
         <f>I33</f>
         <v>522.15970000000004</v>
       </c>
-      <c r="D58" s="1">
+      <c r="E58" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E58" s="11">
+      <c r="F58" s="11">
         <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
-      <c r="F58" s="11">
+      <c r="G58" s="11">
         <f t="shared" si="2"/>
         <v>0.05</v>
       </c>
-      <c r="G58" s="1">
+      <c r="H58" s="1">
         <f t="shared" si="3"/>
         <v>826.39953846153867</v>
       </c>
-      <c r="H58" s="1">
+      <c r="I58" s="1">
         <f t="shared" si="4"/>
         <v>247.91986153846159</v>
       </c>
-      <c r="I58" s="1">
+      <c r="J58" s="1">
         <f t="shared" si="5"/>
         <v>41.319976923076936</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
+    <row r="59" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" t="s">
         <v>3</v>
       </c>
-      <c r="B59">
+      <c r="C59">
         <f>G34</f>
         <v>3</v>
       </c>
-      <c r="C59" s="1">
+      <c r="D59" s="1">
         <f>I34</f>
         <v>490.80950000000001</v>
       </c>
-      <c r="D59" s="1">
+      <c r="E59" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E59" s="11">
+      <c r="F59" s="11">
         <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
-      <c r="F59" s="11">
+      <c r="G59" s="11">
         <f t="shared" si="2"/>
         <v>0.05</v>
       </c>
-      <c r="G59" s="1">
+      <c r="H59" s="1">
         <f t="shared" si="3"/>
         <v>778.16846153846166</v>
       </c>
-      <c r="H59" s="1">
+      <c r="I59" s="1">
         <f t="shared" si="4"/>
         <v>233.45053846153849</v>
       </c>
-      <c r="I59" s="1">
+      <c r="J59" s="1">
         <f t="shared" si="5"/>
         <v>38.908423076923086</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
         <v>27</v>
       </c>
       <c r="B62" s="13"/>
     </row>
-    <row r="63" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
+    <row r="63" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" t="s">
         <v>19</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>9</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>28</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>29</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" t="str">
-        <f>A48</f>
+    <row r="64" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B64" t="str">
+        <f>B48</f>
         <v>Personal Property</v>
       </c>
-      <c r="B64">
-        <f>B48</f>
+      <c r="C64">
+        <f>C48</f>
         <v>1</v>
       </c>
-      <c r="C64" s="1">
-        <f>(C48+$C$44)/(1-$C$41-$C$43)</f>
+      <c r="D64" s="1">
+        <f>(D48+$C$44)/(1-$C$41-$C$43)</f>
         <v>163.87720000000002</v>
       </c>
-      <c r="D64" s="1">
-        <f>(C48+$C$44)/(1-$C$40-$C$43)</f>
+      <c r="E64" s="1">
+        <f>(D48+$C$44)/(1-$C$40-$C$43)</f>
         <v>176.48313846153849</v>
       </c>
-      <c r="E64" s="1">
-        <f>(C48+$C$44)/(1-$C$42-$C$43)</f>
+      <c r="F64" s="1">
+        <f>(D48+$C$44)/(1-$C$42-$C$43)</f>
         <v>191.19006666666667</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" t="str">
-        <f t="shared" ref="A65:B69" si="6">A49</f>
+    <row r="65" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B65" t="str">
+        <f>B49</f>
         <v>Personal Property</v>
       </c>
-      <c r="B65">
-        <f t="shared" si="6"/>
+      <c r="C65">
+        <f>C49</f>
         <v>2</v>
       </c>
-      <c r="C65" s="1">
-        <f t="shared" ref="C65:C75" si="7">(C49+$C$44)/(1-$C$41-$C$43)</f>
+      <c r="D65" s="1">
+        <f>(D49+$C$44)/(1-$C$41-$C$43)</f>
         <v>196.85335714285713</v>
       </c>
-      <c r="D65" s="1">
-        <f t="shared" ref="D65:D75" si="8">(C49+$C$44)/(1-$C$40-$C$43)</f>
+      <c r="E65" s="1">
+        <f>(D49+$C$44)/(1-$C$40-$C$43)</f>
         <v>211.99592307692311</v>
       </c>
-      <c r="E65" s="1">
-        <f t="shared" ref="E65:E72" si="9">(C49+$C$44)/(1-$C$42-$C$43)</f>
+      <c r="F65" s="1">
+        <f>(D49+$C$44)/(1-$C$42-$C$43)</f>
         <v>229.66225</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" t="str">
-        <f t="shared" si="6"/>
+    <row r="66" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B66" t="str">
+        <f>B50</f>
         <v>Personal Property</v>
       </c>
-      <c r="B66">
-        <f t="shared" si="6"/>
+      <c r="C66">
+        <f>C50</f>
         <v>3</v>
       </c>
-      <c r="C66" s="1">
-        <f t="shared" si="7"/>
+      <c r="D66" s="1">
+        <f>(D50+$C$44)/(1-$C$41-$C$43)</f>
         <v>167.59831428571431</v>
       </c>
-      <c r="D66" s="1">
-        <f t="shared" si="8"/>
+      <c r="E66" s="1">
+        <f>(D50+$C$44)/(1-$C$40-$C$43)</f>
         <v>180.49049230769234</v>
       </c>
-      <c r="E66" s="1">
-        <f t="shared" si="9"/>
+      <c r="F66" s="1">
+        <f>(D50+$C$44)/(1-$C$42-$C$43)</f>
         <v>195.53136666666668</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" t="str">
-        <f t="shared" si="6"/>
+    <row r="67" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B67" t="str">
+        <f>B51</f>
         <v>Additional Living Expenses</v>
       </c>
-      <c r="B67">
-        <f t="shared" si="6"/>
+      <c r="C67">
+        <f>C51</f>
         <v>1</v>
       </c>
-      <c r="C67" s="1">
-        <f t="shared" si="7"/>
+      <c r="D67" s="1">
+        <f>(D51+$C$44)/(1-$C$41-$C$43)</f>
         <v>388.18571428571431</v>
       </c>
-      <c r="D67" s="1">
-        <f t="shared" si="8"/>
+      <c r="E67" s="1">
+        <f>(D51+$C$44)/(1-$C$40-$C$43)</f>
         <v>418.04615384615391</v>
       </c>
-      <c r="E67" s="1">
-        <f t="shared" si="9"/>
+      <c r="F67" s="1">
+        <f>(D51+$C$44)/(1-$C$42-$C$43)</f>
         <v>452.88333333333338</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" t="str">
-        <f t="shared" si="6"/>
+    <row r="68" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B68" t="str">
+        <f>B52</f>
         <v>Additional Living Expenses</v>
       </c>
-      <c r="B68">
-        <f t="shared" si="6"/>
+      <c r="C68">
+        <f>C52</f>
         <v>2</v>
       </c>
-      <c r="C68" s="1">
-        <f t="shared" si="7"/>
+      <c r="D68" s="1">
+        <f>(D52+$C$44)/(1-$C$41-$C$43)</f>
         <v>533.55771428571438</v>
       </c>
-      <c r="D68" s="1">
-        <f t="shared" si="8"/>
+      <c r="E68" s="1">
+        <f>(D52+$C$44)/(1-$C$40-$C$43)</f>
         <v>574.60061538461548</v>
       </c>
-      <c r="E68" s="1">
-        <f t="shared" si="9"/>
+      <c r="F68" s="1">
+        <f>(D52+$C$44)/(1-$C$42-$C$43)</f>
         <v>622.48400000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" t="str">
-        <f t="shared" si="6"/>
+    <row r="69" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B69" t="str">
+        <f>B53</f>
         <v>Additional Living Expenses</v>
       </c>
-      <c r="B69">
-        <f t="shared" si="6"/>
+      <c r="C69">
+        <f>C53</f>
         <v>3</v>
       </c>
-      <c r="C69" s="1">
-        <f t="shared" si="7"/>
+      <c r="D69" s="1">
+        <f>(D53+$C$44)/(1-$C$41-$C$43)</f>
         <v>476.57409523809531</v>
       </c>
-      <c r="D69" s="1">
-        <f t="shared" si="8"/>
+      <c r="E69" s="1">
+        <f>(D53+$C$44)/(1-$C$40-$C$43)</f>
         <v>513.23364102564119</v>
       </c>
-      <c r="E69" s="1">
-        <f t="shared" si="9"/>
+      <c r="F69" s="1">
+        <f>(D53+$C$44)/(1-$C$42-$C$43)</f>
         <v>556.00311111111114</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" t="str">
-        <f t="shared" ref="A65:B75" si="10">A54</f>
+    <row r="70" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B70" t="str">
+        <f>B54</f>
         <v>Liability Protection</v>
       </c>
-      <c r="B70">
-        <f t="shared" si="10"/>
+      <c r="C70">
+        <f>C54</f>
         <v>1</v>
       </c>
-      <c r="C70" s="1">
-        <f t="shared" si="7"/>
+      <c r="D70" s="1">
+        <f>(D54+$C$44)/(1-$C$41-$C$43)</f>
         <v>117.86347142857143</v>
       </c>
-      <c r="D70" s="1">
-        <f t="shared" si="8"/>
+      <c r="E70" s="1">
+        <f>(D54+$C$44)/(1-$C$40-$C$43)</f>
         <v>126.92989230769233</v>
       </c>
-      <c r="E70" s="1">
-        <f t="shared" si="9"/>
+      <c r="F70" s="1">
+        <f>(D54+$C$44)/(1-$C$42-$C$43)</f>
         <v>137.50738333333334</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" t="str">
-        <f t="shared" si="10"/>
+    <row r="71" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B71" t="str">
+        <f>B55</f>
         <v>Liability Protection</v>
       </c>
-      <c r="B71">
-        <f t="shared" si="10"/>
+      <c r="C71">
+        <f>C55</f>
         <v>2</v>
       </c>
-      <c r="C71" s="1">
-        <f t="shared" si="7"/>
+      <c r="D71" s="1">
+        <f>(D55+$C$44)/(1-$C$41-$C$43)</f>
         <v>116.3163</v>
       </c>
-      <c r="D71" s="1">
-        <f t="shared" si="8"/>
+      <c r="E71" s="1">
+        <f>(D55+$C$44)/(1-$C$40-$C$43)</f>
         <v>125.2637076923077</v>
       </c>
-      <c r="E71" s="1">
-        <f t="shared" si="9"/>
+      <c r="F71" s="1">
+        <f>(D55+$C$44)/(1-$C$42-$C$43)</f>
         <v>135.70235</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" t="str">
-        <f t="shared" si="10"/>
+    <row r="72" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B72" t="str">
+        <f>B56</f>
         <v>Liability Protection</v>
       </c>
-      <c r="B72">
-        <f t="shared" si="10"/>
+      <c r="C72">
+        <f>C56</f>
         <v>3</v>
       </c>
-      <c r="C72" s="1">
-        <f t="shared" si="7"/>
+      <c r="D72" s="1">
+        <f>(D56+$C$44)/(1-$C$41-$C$43)</f>
         <v>156.58205714285714</v>
       </c>
-      <c r="D72" s="1">
-        <f t="shared" si="8"/>
+      <c r="E72" s="1">
+        <f>(D56+$C$44)/(1-$C$40-$C$43)</f>
         <v>168.62683076923079</v>
       </c>
-      <c r="E72" s="1">
-        <f t="shared" si="9"/>
+      <c r="F72" s="1">
+        <f>(D56+$C$44)/(1-$C$42-$C$43)</f>
         <v>182.67906666666667</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" t="str">
-        <f t="shared" si="10"/>
+    <row r="73" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B73" t="str">
+        <f>B57</f>
         <v>Guest Medical Protection</v>
       </c>
-      <c r="B73">
-        <f t="shared" si="10"/>
+      <c r="C73">
+        <f>C57</f>
         <v>1</v>
       </c>
-      <c r="C73" s="1">
-        <f t="shared" si="7"/>
+      <c r="D73" s="1">
+        <f>(D57+$C$44)/(1-$C$41-$C$43)</f>
         <v>530.649</v>
       </c>
-      <c r="D73" s="1">
-        <f t="shared" si="8"/>
+      <c r="E73" s="1">
+        <f>(D57+$C$44)/(1-$C$40-$C$43)</f>
         <v>571.46815384615388</v>
       </c>
-      <c r="E73" s="1">
-        <f t="shared" ref="E73:E75" si="11">(C57+$C$44)/(1-$C$42-$C$43)</f>
+      <c r="F73" s="1">
+        <f>(D57+$C$44)/(1-$C$42-$C$43)</f>
         <v>619.09050000000002</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" t="str">
-        <f t="shared" si="10"/>
+    <row r="74" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B74" t="str">
+        <f>B58</f>
         <v>Guest Medical Protection</v>
       </c>
-      <c r="B74">
-        <f t="shared" si="10"/>
+      <c r="C74">
+        <f>C58</f>
         <v>2</v>
       </c>
-      <c r="C74" s="1">
-        <f t="shared" si="7"/>
+      <c r="D74" s="1">
+        <f>(D58+$C$44)/(1-$C$41-$C$43)</f>
         <v>767.37100000000009</v>
       </c>
-      <c r="D74" s="1">
-        <f t="shared" si="8"/>
+      <c r="E74" s="1">
+        <f>(D58+$C$44)/(1-$C$40-$C$43)</f>
         <v>826.39953846153867</v>
       </c>
-      <c r="E74" s="1">
-        <f t="shared" si="11"/>
+      <c r="F74" s="1">
+        <f>(D58+$C$44)/(1-$C$42-$C$43)</f>
         <v>895.26616666666678</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" t="str">
-        <f t="shared" si="10"/>
+    <row r="75" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B75" t="str">
+        <f>B59</f>
         <v>Guest Medical Protection</v>
       </c>
-      <c r="B75">
-        <f t="shared" si="10"/>
+      <c r="C75">
+        <f>C59</f>
         <v>3</v>
       </c>
-      <c r="C75" s="1">
-        <f t="shared" si="7"/>
+      <c r="D75" s="1">
+        <f>(D59+$C$44)/(1-$C$41-$C$43)</f>
         <v>722.58500000000004</v>
       </c>
-      <c r="D75" s="1">
-        <f t="shared" si="8"/>
+      <c r="E75" s="1">
+        <f>(D59+$C$44)/(1-$C$40-$C$43)</f>
         <v>778.16846153846166</v>
       </c>
-      <c r="E75" s="1">
-        <f t="shared" si="11"/>
+      <c r="F75" s="1">
+        <f>(D59+$C$44)/(1-$C$42-$C$43)</f>
         <v>843.01583333333338</v>
       </c>
     </row>
